--- a/docs/lift-log-program-template.xlsx
+++ b/docs/lift-log-program-template.xlsx
@@ -2530,7 +2530,7 @@
       <c r="J201" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" deleteColumns="0" sort="0" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D201">
       <formula1>"Chest,Front delts,Side delts,Rear delts,Triceps,Lats,Upper back,Traps,Biceps,Forearms,Quads,Hamstrings,Glutes,Adductors,Abductors,Calves,Abs,Obliques,Lower back,Neck"</formula1>
